--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1189,7 +1189,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1379,7 +1379,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1450,7 +1450,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>適用されるターゲット参照母集団のどの部分を示すコード。たとえば、通常または治療範囲。 / Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
@@ -1635,7 +1635,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -1997,7 +1997,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="65.90625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2912" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="530">
   <si>
     <t>Property</t>
   </si>
@@ -1273,7 +1273,10 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -8119,9 +8122,11 @@
       <c r="X51" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="Y51" s="2"/>
+      <c r="Y51" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8157,27 +8162,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8203,16 +8208,16 @@
         <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8240,10 +8245,10 @@
         <v>403</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8261,7 +8266,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8282,10 +8287,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8296,10 +8301,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8322,16 +8327,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8381,7 +8386,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8399,27 +8404,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8442,16 +8447,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8501,7 +8506,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8519,27 +8524,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8562,19 +8567,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8623,7 +8628,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8635,7 +8640,7 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8644,10 +8649,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8658,10 +8663,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8776,10 +8781,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8896,14 +8901,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8925,10 +8930,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -8983,7 +8988,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9018,10 +9023,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9044,13 +9049,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9101,7 +9106,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9110,7 +9115,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9122,10 +9127,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9136,10 +9141,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9162,13 +9167,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9219,7 +9224,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9228,7 +9233,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9240,10 +9245,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9254,10 +9259,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9283,16 +9288,16 @@
         <v>188</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9320,10 +9325,10 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9341,7 +9346,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9359,10 +9364,10 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>391</v>
@@ -9376,10 +9381,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9405,16 +9410,16 @@
         <v>188</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9442,10 +9447,10 @@
         <v>403</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9463,7 +9468,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9481,10 +9486,10 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>391</v>
@@ -9498,10 +9503,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9524,17 +9529,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9583,7 +9588,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9607,7 +9612,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9618,10 +9623,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9647,10 +9652,10 @@
         <v>206</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9701,7 +9706,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9722,10 +9727,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9736,10 +9741,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9762,16 +9767,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9821,7 +9826,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9842,10 +9847,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9856,10 +9861,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9882,16 +9887,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9941,7 +9946,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9962,10 +9967,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -9976,10 +9981,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10002,19 +10007,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10063,7 +10068,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10084,10 +10089,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10098,10 +10103,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10216,10 +10221,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10336,14 +10341,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10365,10 +10370,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10423,7 +10428,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10458,10 +10463,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10487,13 +10492,13 @@
         <v>188</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O71" t="s" s="2">
         <v>305</v>
@@ -10543,7 +10548,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10561,7 +10566,7 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>309</v>
@@ -10578,10 +10583,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10607,13 +10612,13 @@
         <v>364</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>367</v>
@@ -10665,7 +10670,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10683,7 +10688,7 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>370</v>
@@ -10700,10 +10705,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10729,13 +10734,13 @@
         <v>188</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>376</v>
@@ -10787,7 +10792,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10822,10 +10827,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10851,16 +10856,16 @@
         <v>188</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10909,7 +10914,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10944,10 +10949,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10973,16 +10978,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11031,7 +11036,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11052,10 +11057,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
